--- a/results/job_matches_2026-05-07.xlsx
+++ b/results/job_matches_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Health Account Intern</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
+          <t>https://www.indeed.com/viewjob?jk=b4c4141e761a1d57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Health Account Intern</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4c4141e761a1d57</t>
+          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
+          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
+          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Databricks Engineer and Architect</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
+          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Databricks Engineer and Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
+          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=c43843e3963f6e92</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43843e3963f6e92</t>
+          <t>https://www.indeed.com/viewjob?jk=df1902d36083d34f</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1902d36083d34f</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb867686433b7a1</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb867686433b7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=3aeafc948a2f0f6c</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aeafc948a2f0f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=c45b322f3e5694ad</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,69 +1116,69 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Blob Storage, GCP, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45b322f3e5694ad</t>
+          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>Cambridge Mobile Telematics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Blob Storage, GCP, PostgreSQL</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
+          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cambridge Mobile Telematics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
+          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Backend (Python)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
+          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Backend (Python)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
+          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
+          <t>https://www.indeed.com/viewjob?jk=0c3ebd29f25c3c6c</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c3ebd29f25c3c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb9808701c11641</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb9808701c11641</t>
+          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>SOFTILITY INC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
+          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SOFTILITY INC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
+          <t>https://www.indeed.com/viewjob?jk=bb10f4ead0ebaa8c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
+          <t>https://www.indeed.com/viewjob?jk=84ff26ed72edcf59</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data analyst</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7e583a5ea56607</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d23da7e95a1130</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Blizzard Entertainment</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
+          <t>https://www.indeed.com/viewjob?jk=d78d5b077f1a5305</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=75bd1c4231899eca</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cloud Ramp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=015ea5d5c6dc0865</t>
+          <t>https://www.indeed.com/viewjob?jk=465359694837863c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kankakee, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
+          <t>https://www.indeed.com/viewjob?jk=51caa710f04f77dc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
+          <t>https://www.indeed.com/viewjob?jk=147bab346b137aef</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>vectorsoft</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1777,11 +1777,11 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bdce3e69ca5f6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f5a5f35444067b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb3e3385b26a0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b4c20fd299a5c2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
+          <t>https://www.indeed.com/viewjob?jk=6e08ec2e44f47101</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Multi-Cloud Network Architect V</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, Oracle</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9384fbb0ce6b583b</t>
+          <t>https://www.indeed.com/viewjob?jk=058204891b516db6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DATA SCIENTIST</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Tableau, CI/CD, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdfc9f08c573bf84</t>
+          <t>https://www.indeed.com/viewjob?jk=236c6d8ffa19b4d8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Engineer - (Java, Data, Enterprise Platforms &amp; Systems Integration) *HYBRID*</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd8c2b6d2b269c99</t>
+          <t>https://www.indeed.com/viewjob?jk=c8001dc6417b644e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=182574da3c06479e</t>
+          <t>https://www.indeed.com/viewjob?jk=37726abce257e377</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b0e598b9832c43</t>
+          <t>https://www.indeed.com/viewjob?jk=26524036d8b7988d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Terra Quantum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
+          <t>https://www.indeed.com/viewjob?jk=14335716af5e911f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61fd67550df6c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2fc4d512bb1973</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59fae488bfb069d7</t>
+          <t>https://www.indeed.com/viewjob?jk=7f44960818abf6fa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c511d00669b005c9</t>
+          <t>https://www.indeed.com/viewjob?jk=38df319950eca972</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e02714fa8eb1d57</t>
+          <t>https://www.indeed.com/viewjob?jk=11d1ad5bd44efc7d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineering - E&amp;P - Data Integration Engineer I</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3c21492b139248</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
+          <t>https://www.indeed.com/viewjob?jk=91408b290dbe3655</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,102 +2316,102 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3f967eb48c6c658d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Clayco</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb294057a60f547</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Laural Parke</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19dac2449c2108f4</t>
+          <t>https://www.indeed.com/viewjob?jk=f32cb97309ddc35f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Revelation Pharma</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265eee1218fa6fae</t>
+          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ce310e3e5771dd</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Networking Consultant</t>
+          <t>Mid- Level Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Blizzard Entertainment</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
+          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Cloud Ramp</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
+          <t>https://www.indeed.com/viewjob?jk=015ea5d5c6dc0865</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Entry-Level Cloud Engineering Specialist</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d9f4abcf179d24</t>
+          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>vectorsoft</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390498da25e9e01</t>
+          <t>https://www.indeed.com/viewjob?jk=3bdce3e69ca5f6c4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SSIS / Azure Data Factory Engineer</t>
+          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kankakee, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c3cae0c83282a2</t>
+          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tardus inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c45bbb6f084151</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb3e3385b26a0b5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Biloxi 5139</t>
+          <t>Senior Software Engineer - Cloud Gateway</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Keesler Federal Credit Union</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Biloxi, MS, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=923871eb4e708d96</t>
+          <t>https://www.indeed.com/viewjob?jk=7b72e865e6bee153</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>DASi LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
+          <t>https://www.indeed.com/viewjob?jk=744c7eb16a44dfd7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Multi-Cloud Network Architect V</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, Oracle</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=282fdfffaf16a91c</t>
+          <t>https://www.indeed.com/viewjob?jk=9384fbb0ce6b583b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IT/OT Data Engineer</t>
+          <t>Senior Engineer - (Java, Data, Enterprise Platforms &amp; Systems Integration) *HYBRID*</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c53f35832dc5e29</t>
+          <t>https://www.indeed.com/viewjob?jk=bd8c2b6d2b269c99</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mesa Labs</t>
+          <t>Mustang Cat</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d54ee3197b525a</t>
+          <t>https://www.indeed.com/viewjob?jk=182574da3c06479e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps Mobile</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,102 +2946,102 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=52b0e598b9832c43</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Terra Quantum</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
+          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Data Architect Specialist</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SAMYANG AMERICA INC</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brea, CA, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
+          <t>https://www.indeed.com/viewjob?jk=b61fd67550df6c0b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
+          <t>https://www.indeed.com/viewjob?jk=59fae488bfb069d7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=c511d00669b005c9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e02714fa8eb1d57</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76b38f99ba86c67f</t>
+          <t>https://www.indeed.com/viewjob?jk=c01266825391c4b2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3ffcafc747cce2</t>
+          <t>https://www.indeed.com/viewjob?jk=a6d53a6f5df85230</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,102 +3226,102 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fefa13594369c9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
+          <t>https://www.indeed.com/viewjob?jk=5f05f8c3822801d0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
+          <t>https://www.indeed.com/viewjob?jk=e5cb254b6fa4c90d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=a1023da172f564b3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,67 +3366,67 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
+          <t>https://www.indeed.com/viewjob?jk=569a8ebe7a6a04fb</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BigData Platform Admin (Hadoop)-2</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e582bed3ddb8ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5760a75e3ce777</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Track 25 LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,242 +3436,242 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
+          <t>https://www.indeed.com/viewjob?jk=06b22890290d9506</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Integration Software Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b035b944f2ad4c37</t>
+          <t>https://www.indeed.com/viewjob?jk=6d137efe54ff8dc9</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Integration Software Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba6e4aacd5b6631</t>
+          <t>https://www.indeed.com/viewjob?jk=8e7bf8442a8bdc8c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Integration Software Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c7e0f49df408be</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a0f6c9e311fc83</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Integration Software Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93164fc43ac74193</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4d775401ea97c2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Integration Software Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12a4fd124772d9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b3fe13a7719868</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Integration Software Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c38e2fae9b46f905</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbae8d56e4e939a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
+          <t>https://www.indeed.com/viewjob?jk=5637bcb1e7b43c44</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Onspring Technologies, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
+          <t>https://www.indeed.com/viewjob?jk=2a4765c52a051877</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI Applications Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SEEQ</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ed320077d234a1</t>
+          <t>https://www.indeed.com/viewjob?jk=48f4ac34ad3bcf5d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c923560ebd174d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,40 +3821,3015 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
+          <t>https://www.indeed.com/viewjob?jk=7747c9538f008641</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13b93b608c2e5719</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51bb38b62986fdc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7458fc8ef3b94ba4</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c2fef802ccfc9d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3acbd4afc720980</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7dcc086d91c5f3f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27889ab1b19cdbb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04d97aef53cbdb38</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06f0993bba5c0363</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8660ca070b0a4e40</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=478a3c82f44b4c92</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f74fca29cf6b21c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fb9910261cebda6</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=111aee837e77fae4</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3920a8488c303cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=275b3a26137e4026</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7ffec4a653d9ae3</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f44aa9758e0b8c30</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea2bccc7e52cd86a</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84325aa611216471</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4a28317818b7105</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24ce7897ab593fa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45f0b2358693b4b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d37cebaf46b00d4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d0b4a8c187dbd0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44c10e4b59da5a27</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=147d735cf2c8585c</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec72c554d7db0f5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4062754ea30ea206</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=694133283d3d475b</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5087395011639826</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b09dac1045556912</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Snowflake Developer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=791202dbdbb21c1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Data Engineering - E&amp;P - Data Integration Engineer I</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Genesis Global Group</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Myrtle Point, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Cloud Network Architect</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Azure Network Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Laural Parke</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19dac2449c2108f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>DevOps / AgentOps Engineer</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Revelation Pharma</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=265eee1218fa6fae</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5f621c8ad4f69fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8ce310e3e5771dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>FirstNet Global</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Napa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Klaxontech</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Cloud Networking Consultant</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Montefiore Einstein</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Yonkers, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer IV</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Cambia Health Solutions</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Sr. Software Systems and Data Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=606b5659a9dfdc90</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Entry-Level Cloud Engineering Specialist</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43d9f4abcf179d24</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Data Engineer with Python</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Tardus inc</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80c45bbb6f084151</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer- MSI</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>The Baldwin Group</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57ba967c2292803c</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Data Scientist, AI Data Foundations</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>MeridianLink</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2390498da25e9e01</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>SSIS / Azure Data Factory Engineer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85c3cae0c83282a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer Biloxi 5139</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Keesler Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Biloxi, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=923871eb4e708d96</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Application Security Engineer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Centerfield</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, GCP, Scala, CI/CD, Jenkins, Kubernetes, AKS, Jenkins</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44d5251e8c79cc0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Data Analyst — AI-Driven Insights</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>David's Bridal</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>IT/OT Data Engineer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Merz Aesthetics</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Racine, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c53f35832dc5e29</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Mesa Labs</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Lakewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71d54ee3197b525a</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Software Engineer - DevOps Mobile</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Staples</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Framingham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Data Scientist, AI Data Foundations</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>MeridianLink</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Data Architect (Snowflake)</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Mango Chamba, LLC</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76b38f99ba86c67f</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Advisor Solution Architect</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Gainwell Technologies LLC</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Checkmate</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Montefiore Einstein</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Yonkers, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a3ffcafc747cce2</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>FastAPI</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>BigData Platform Admin (Hadoop)-2</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e582bed3ddb8ed5</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Senior .NET Engineer</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Navigate360</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Richfield, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=173985f052eba684</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Track 25 LLC</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Mesa, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>AI Application Developer III</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Love’s Travel Stops</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>AI Application Developer III -Houston, TX</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Love’s Travel Stops</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Senior Data Integration Software Engineer</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b035b944f2ad4c37</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Senior Data Integration Software Engineer</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ba6e4aacd5b6631</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Data Integration Software Engineer</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Portsmouth, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4c7e0f49df408be</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Senior Data Integration Software Engineer</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Portsmouth, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93164fc43ac74193</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Data Integration Software Engineer</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12a4fd124772d9d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Data Integration Software Engineer</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c38e2fae9b46f905</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Litera</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Onspring Technologies, LLC</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Full-Stack (Factory Systems)</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68c700567606c4e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>AI Applications Engineer</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SEEQ</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02ed320077d234a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Enterprise AI Architect</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Radwell International</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Willingboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
           <t>Senior Engineer, AI</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>Harman</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C183" t="inlineStr">
         <is>
           <t>Novi, MI, US USA</t>
         </is>
       </c>
-      <c r="D98" t="n">
+      <c r="D183" t="n">
         <v>10.4</v>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E183" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Databricks, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F183" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G183" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4a91d05d9ba98a3a</t>
         </is>

--- a/results/job_matches_2026-05-07.xlsx
+++ b/results/job_matches_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G183"/>
+  <dimension ref="A1:G178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Health Account Intern</t>
+          <t>Compliance, Senior Backend Engineer (Java &amp; ETL Specialist), Dallas, Associate</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
+          <t>https://www.indeed.com/viewjob?jk=e21fade0470597e2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Compliance, Senior Backend Engineer (Java &amp; ETL Specialist), Dallas, Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21fade0470597e2</t>
+          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Databricks Engineer and Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
+          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
+          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Databricks Engineer and Architect</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
+          <t>https://www.indeed.com/viewjob?jk=c43843e3963f6e92</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,122 +941,122 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Blob Storage, GCP, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43843e3963f6e92</t>
+          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cambridge Mobile Telematics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1902d36083d34f</t>
+          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb867686433b7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend (Python)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aeafc948a2f0f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
         </is>
       </c>
     </row>
@@ -1068,90 +1068,90 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45b322f3e5694ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Blob Storage, GCP, PostgreSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
+          <t>https://www.indeed.com/viewjob?jk=0c3ebd29f25c3c6c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cambridge Mobile Telematics</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb9808701c11641</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
+          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Backend (Python)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SOFTILITY INC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
+          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
+          <t>https://www.indeed.com/viewjob?jk=bb10f4ead0ebaa8c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c3ebd29f25c3c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=84ff26ed72edcf59</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb9808701c11641</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7e583a5ea56607</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d23da7e95a1130</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SOFTILITY INC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d78d5b077f1a5305</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
+          <t>https://www.indeed.com/viewjob?jk=75bd1c4231899eca</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb10f4ead0ebaa8c</t>
+          <t>https://www.indeed.com/viewjob?jk=465359694837863c</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ff26ed72edcf59</t>
+          <t>https://www.indeed.com/viewjob?jk=51caa710f04f77dc</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7e583a5ea56607</t>
+          <t>https://www.indeed.com/viewjob?jk=147bab346b137aef</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d23da7e95a1130</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f5a5f35444067b</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d78d5b077f1a5305</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b4c20fd299a5c2</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75bd1c4231899eca</t>
+          <t>https://www.indeed.com/viewjob?jk=6e08ec2e44f47101</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=465359694837863c</t>
+          <t>https://www.indeed.com/viewjob?jk=058204891b516db6</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51caa710f04f77dc</t>
+          <t>https://www.indeed.com/viewjob?jk=236c6d8ffa19b4d8</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147bab346b137aef</t>
+          <t>https://www.indeed.com/viewjob?jk=c8001dc6417b644e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f5a5f35444067b</t>
+          <t>https://www.indeed.com/viewjob?jk=37726abce257e377</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b4c20fd299a5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=26524036d8b7988d</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e08ec2e44f47101</t>
+          <t>https://www.indeed.com/viewjob?jk=14335716af5e911f</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058204891b516db6</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2fc4d512bb1973</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=236c6d8ffa19b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=7f44960818abf6fa</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8001dc6417b644e</t>
+          <t>https://www.indeed.com/viewjob?jk=38df319950eca972</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37726abce257e377</t>
+          <t>https://www.indeed.com/viewjob?jk=11d1ad5bd44efc7d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26524036d8b7988d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3c21492b139248</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14335716af5e911f</t>
+          <t>https://www.indeed.com/viewjob?jk=91408b290dbe3655</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2fc4d512bb1973</t>
+          <t>https://www.indeed.com/viewjob?jk=3f967eb48c6c658d</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f44960818abf6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb294057a60f547</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38df319950eca972</t>
+          <t>https://www.indeed.com/viewjob?jk=f32cb97309ddc35f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE)</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d1ad5bd44efc7d</t>
+          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE)</t>
+          <t>Senior Data analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3c21492b139248</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE)</t>
+          <t>Mid- Level Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91408b290dbe3655</t>
+          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE)</t>
+          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Blizzard Entertainment</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f967eb48c6c658d</t>
+          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE)</t>
+          <t>IT Specialist/Systems Administrator</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>QUALGEN, LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb294057a60f547</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e0e141efc8c345</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE)</t>
+          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32cb97309ddc35f</t>
+          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cloud Ramp</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
+          <t>https://www.indeed.com/viewjob?jk=015ea5d5c6dc0865</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data analyst</t>
+          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Kankakee, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
+          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
+          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blizzard Entertainment</t>
+          <t>vectorsoft</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
+          <t>https://www.indeed.com/viewjob?jk=3bdce3e69ca5f6c4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb3e3385b26a0b5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Senior Software Engineer - Cloud Gateway</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cloud Ramp</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=015ea5d5c6dc0865</t>
+          <t>https://www.indeed.com/viewjob?jk=7b72e865e6bee153</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>data engineer sr- ST; Nashville, TN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
+          <t>https://www.indeed.com/viewjob?jk=740c3688a7f68b22</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>vectorsoft</t>
+          <t>DASi LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bdce3e69ca5f6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=744c7eb16a44dfd7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
+          <t>Multi-Cloud Network Architect V</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kankakee, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, Oracle</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9384fbb0ce6b583b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mustang Cat</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb3e3385b26a0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=182574da3c06479e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Gateway</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b72e865e6bee153</t>
+          <t>https://www.indeed.com/viewjob?jk=52b0e598b9832c43</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DASi LLC</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744c7eb16a44dfd7</t>
+          <t>https://www.indeed.com/viewjob?jk=b61fd67550df6c0b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Multi-Cloud Network Architect V</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, Oracle</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9384fbb0ce6b583b</t>
+          <t>https://www.indeed.com/viewjob?jk=59fae488bfb069d7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Engineer - (Java, Data, Enterprise Platforms &amp; Systems Integration) *HYBRID*</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd8c2b6d2b269c99</t>
+          <t>https://www.indeed.com/viewjob?jk=c511d00669b005c9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=182574da3c06479e</t>
+          <t>https://www.indeed.com/viewjob?jk=9e02714fa8eb1d57</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b0e598b9832c43</t>
+          <t>https://www.indeed.com/viewjob?jk=c01266825391c4b2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Terra Quantum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
+          <t>https://www.indeed.com/viewjob?jk=a6d53a6f5df85230</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61fd67550df6c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fefa13594369c9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59fae488bfb069d7</t>
+          <t>https://www.indeed.com/viewjob?jk=5f05f8c3822801d0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c511d00669b005c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e5cb254b6fa4c90d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e02714fa8eb1d57</t>
+          <t>https://www.indeed.com/viewjob?jk=a1023da172f564b3</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01266825391c4b2</t>
+          <t>https://www.indeed.com/viewjob?jk=569a8ebe7a6a04fb</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6d53a6f5df85230</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5760a75e3ce777</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fefa13594369c9</t>
+          <t>https://www.indeed.com/viewjob?jk=06b22890290d9506</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f05f8c3822801d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6d137efe54ff8dc9</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5cb254b6fa4c90d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e7bf8442a8bdc8c</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1023da172f564b3</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a0f6c9e311fc83</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=569a8ebe7a6a04fb</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4d775401ea97c2</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5760a75e3ce777</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b3fe13a7719868</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b22890290d9506</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbae8d56e4e939a</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d137efe54ff8dc9</t>
+          <t>https://www.indeed.com/viewjob?jk=5637bcb1e7b43c44</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e7bf8442a8bdc8c</t>
+          <t>https://www.indeed.com/viewjob?jk=2a4765c52a051877</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a0f6c9e311fc83</t>
+          <t>https://www.indeed.com/viewjob?jk=48f4ac34ad3bcf5d</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4d775401ea97c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c923560ebd174d</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b3fe13a7719868</t>
+          <t>https://www.indeed.com/viewjob?jk=7747c9538f008641</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbae8d56e4e939a</t>
+          <t>https://www.indeed.com/viewjob?jk=13b93b608c2e5719</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5637bcb1e7b43c44</t>
+          <t>https://www.indeed.com/viewjob?jk=51bb38b62986fdc6</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a4765c52a051877</t>
+          <t>https://www.indeed.com/viewjob?jk=7458fc8ef3b94ba4</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f4ac34ad3bcf5d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2fef802ccfc9d0</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c923560ebd174d</t>
+          <t>https://www.indeed.com/viewjob?jk=a3acbd4afc720980</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,14 +3821,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7747c9538f008641</t>
+          <t>https://www.indeed.com/viewjob?jk=7dcc086d91c5f3f2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b93b608c2e5719</t>
+          <t>https://www.indeed.com/viewjob?jk=27889ab1b19cdbb7</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51bb38b62986fdc6</t>
+          <t>https://www.indeed.com/viewjob?jk=04d97aef53cbdb38</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7458fc8ef3b94ba4</t>
+          <t>https://www.indeed.com/viewjob?jk=06f0993bba5c0363</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2fef802ccfc9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=8660ca070b0a4e40</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,14 +3996,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3acbd4afc720980</t>
+          <t>https://www.indeed.com/viewjob?jk=478a3c82f44b4c92</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE) Consultant</t>
+          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dcc086d91c5f3f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f74fca29cf6b21c4</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27889ab1b19cdbb7</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb9910261cebda6</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d97aef53cbdb38</t>
+          <t>https://www.indeed.com/viewjob?jk=111aee837e77fae4</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f0993bba5c0363</t>
+          <t>https://www.indeed.com/viewjob?jk=d3920a8488c303cf</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8660ca070b0a4e40</t>
+          <t>https://www.indeed.com/viewjob?jk=275b3a26137e4026</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=478a3c82f44b4c92</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ffec4a653d9ae3</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f74fca29cf6b21c4</t>
+          <t>https://www.indeed.com/viewjob?jk=f44aa9758e0b8c30</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb9910261cebda6</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2bccc7e52cd86a</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111aee837e77fae4</t>
+          <t>https://www.indeed.com/viewjob?jk=84325aa611216471</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3920a8488c303cf</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a28317818b7105</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=275b3a26137e4026</t>
+          <t>https://www.indeed.com/viewjob?jk=24ce7897ab593fa4</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ffec4a653d9ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=45f0b2358693b4b1</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44aa9758e0b8c30</t>
+          <t>https://www.indeed.com/viewjob?jk=d37cebaf46b00d4e</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2bccc7e52cd86a</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0b4a8c187dbd0a</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84325aa611216471</t>
+          <t>https://www.indeed.com/viewjob?jk=44c10e4b59da5a27</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a28317818b7105</t>
+          <t>https://www.indeed.com/viewjob?jk=147d735cf2c8585c</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ce7897ab593fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=ec72c554d7db0f5f</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f0b2358693b4b1</t>
+          <t>https://www.indeed.com/viewjob?jk=4062754ea30ea206</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37cebaf46b00d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=694133283d3d475b</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0b4a8c187dbd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=5087395011639826</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44c10e4b59da5a27</t>
+          <t>https://www.indeed.com/viewjob?jk=b09dac1045556912</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147d735cf2c8585c</t>
+          <t>https://www.indeed.com/viewjob?jk=791202dbdbb21c1d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+          <t>Data Engineering - E&amp;P - Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec72c554d7db0f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4062754ea30ea206</t>
+          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,67 +4871,67 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694133283d3d475b</t>
+          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Laural Parke</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5087395011639826</t>
+          <t>https://www.indeed.com/viewjob?jk=19dac2449c2108f4</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer (FDE) Senior Consultant</t>
+          <t>DevOps / AgentOps Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Revelation Pharma</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09dac1045556912</t>
+          <t>https://www.indeed.com/viewjob?jk=265eee1218fa6fae</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791202dbdbb21c1d</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f621c8ad4f69fd</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Engineering - E&amp;P - Data Integration Engineer I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ce310e3e5771dd</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
+          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
+          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Networking Consultant</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Laural Parke</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19dac2449c2108f4</t>
+          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Revelation Pharma</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265eee1218fa6fae</t>
+          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Senior Data Engineer- MSI</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f621c8ad4f69fd</t>
+          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Systems and Data Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,32 +5221,32 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ce310e3e5771dd</t>
+          <t>https://www.indeed.com/viewjob?jk=606b5659a9dfdc90</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,32 +5256,32 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=57ba967c2292803c</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Entry-Level Cloud Engineering Specialist</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,32 +5291,32 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
+          <t>https://www.indeed.com/viewjob?jk=43d9f4abcf179d24</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Cloud Networking Consultant</t>
+          <t>Data Scientist, AI Data Foundations</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,32 +5326,32 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
+          <t>https://www.indeed.com/viewjob?jk=2390498da25e9e01</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>SSIS / Azure Data Factory Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
+          <t>https://www.indeed.com/viewjob?jk=85c3cae0c83282a2</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Platform Engineer IV</t>
+          <t>Data Engineer with Python</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Tardus inc</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=80c45bbb6f084151</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Sr. Software Systems and Data Engineer</t>
+          <t>Senior Data Engineer Biloxi 5139</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Keesler Federal Credit Union</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Biloxi, MS, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b5659a9dfdc90</t>
+          <t>https://www.indeed.com/viewjob?jk=923871eb4e708d96</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Entry-Level Cloud Engineering Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d9f4abcf179d24</t>
+          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>Data Platform Engineer IV</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Tardus inc</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c45bbb6f084151</t>
+          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- MSI</t>
+          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
+          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Security Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Centerfield</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, Tableau, CI/CD</t>
+          <t>AWS, ECS, RDS, GCP, Scala, CI/CD, Jenkins, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,19 +5571,19 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ba967c2292803c</t>
+          <t>https://www.indeed.com/viewjob?jk=44d5251e8c79cc0b</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390498da25e9e01</t>
+          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SSIS / Azure Data Factory Engineer</t>
+          <t>IT/OT Data Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c3cae0c83282a2</t>
+          <t>https://www.indeed.com/viewjob?jk=3c53f35832dc5e29</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Biloxi 5139</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Keesler Federal Credit Union</t>
+          <t>Mesa Labs</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Biloxi, MS, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=923871eb4e708d96</t>
+          <t>https://www.indeed.com/viewjob?jk=71d54ee3197b525a</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - DevOps Mobile</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
+          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Application Security Engineer</t>
+          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Centerfield</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, CI/CD, Jenkins, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d5251e8c79cc0b</t>
+          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
+          <t>https://www.indeed.com/viewjob?jk=76b38f99ba86c67f</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>IT/OT Data Engineer</t>
+          <t>Data Scientist, AI Data Foundations</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c53f35832dc5e29</t>
+          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Mesa Labs</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,102 +5851,102 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d54ee3197b525a</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps Mobile</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Amer Technology, Inc</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=46b3557dd6a86d77</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3ffcafc747cce2</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,32 +5956,32 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,32 +5991,32 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Advisor Solution Architect</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,32 +6026,32 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
+          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76b38f99ba86c67f</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>BigData Platform Admin (Hadoop)-2</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,34 +6086,34 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=0e582bed3ddb8ed5</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
+          <t>https://www.indeed.com/viewjob?jk=24e6c09a79e3dceb</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior .NET Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Navigate360</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Richfield, OH, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3ffcafc747cce2</t>
+          <t>https://www.indeed.com/viewjob?jk=173985f052eba684</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Track 25 LLC</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
+          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BigData Platform Admin (Hadoop)-2</t>
+          <t>AI Application Developer III</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e582bed3ddb8ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior .NET Engineer</t>
+          <t>AI Application Developer III -Houston, TX</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Navigate360</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Richfield, OH, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,34 +6261,34 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173985f052eba684</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Applications Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Track 25 LLC</t>
+          <t>SEEQ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
+          <t>https://www.indeed.com/viewjob?jk=02ed320077d234a1</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>Senior Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,34 +6331,34 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
+          <t>https://www.indeed.com/viewjob?jk=b035b944f2ad4c37</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>Senior Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,24 +6366,24 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba6e4aacd5b6631</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior Data Integration Software Engineer</t>
+          <t>Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b035b944f2ad4c37</t>
+          <t>https://www.indeed.com/viewjob?jk=c4c7e0f49df408be</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba6e4aacd5b6631</t>
+          <t>https://www.indeed.com/viewjob?jk=93164fc43ac74193</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,14 +6481,14 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c7e0f49df408be</t>
+          <t>https://www.indeed.com/viewjob?jk=12a4fd124772d9d2</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Senior Data Integration Software Engineer</t>
+          <t>Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93164fc43ac74193</t>
+          <t>https://www.indeed.com/viewjob?jk=c38e2fae9b46f905</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Data Integration Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,34 +6541,34 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12a4fd124772d9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Data Integration Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Onspring Technologies, LLC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,34 +6576,34 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c38e2fae9b46f905</t>
+          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr. Software Engineer, Full-Stack (Factory Systems)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
+          <t>https://www.indeed.com/viewjob?jk=68c700567606c4e9</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer, AI</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Onspring Technologies, LLC</t>
+          <t>Harman</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Novi, MI, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,190 +6646,15 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Full-Stack (Factory Systems)</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68c700567606c4e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>AI Applications Engineer</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>SEEQ</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02ed320077d234a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Enterprise AI Architect</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Radwell International</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Willingboro, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Senior Engineer, AI</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Harman</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Novi, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4a91d05d9ba98a3a</t>
         </is>

--- a/results/job_matches_2026-05-07.xlsx
+++ b/results/job_matches_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,60 +538,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Azure, Databricks</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9377a4724bf38c</t>
+          <t>https://www.indeed.com/viewjob?jk=7283c54206f1c1eb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JCPenney</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2579776810e54bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9377a4724bf38c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Data Engineer- Local</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JCPenney</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d51b3269206c63f</t>
+          <t>https://www.indeed.com/viewjob?jk=98a4e4b94b73fdc3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JCPenney</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4c4141e761a1d57</t>
+          <t>https://www.indeed.com/viewjob?jk=2579776810e54bb8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Compliance, Senior Backend Engineer (Java &amp; ETL Specialist), Dallas, Associate</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>JCPenney</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21fade0470597e2</t>
+          <t>https://www.indeed.com/viewjob?jk=3d51b3269206c63f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
+          <t>https://www.indeed.com/viewjob?jk=b4c4141e761a1d57</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Compliance, Senior Backend Engineer (Java &amp; ETL Specialist), Dallas, Associate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=e21fade0470597e2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
+          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>AI Research Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Scala, Splunk</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448348a55cfb6b88</t>
+          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2490ff4694380e91</t>
+          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,137 +951,137 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43843e3963f6e92</t>
+          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cambridge Mobile Telematics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Scala, Splunk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
+          <t>https://www.indeed.com/viewjob?jk=448348a55cfb6b88</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c3ebd29f25c3c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2490ff4694380e91</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb9808701c11641</t>
+          <t>https://www.indeed.com/viewjob?jk=c43843e3963f6e92</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Cambridge Mobile Telematics</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
+          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb10f4ead0ebaa8c</t>
+          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
+          <t>https://www.indeed.com/viewjob?jk=0c3ebd29f25c3c6c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data analyst</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb9808701c11641</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
+          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=bb10f4ead0ebaa8c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cloud Ramp</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=015ea5d5c6dc0865</t>
+          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
+          <t>Senior Data analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kankakee, IL, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Mid- Level Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
+          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>vectorsoft</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bdce3e69ca5f6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cloud Ramp</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb3e3385b26a0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=015ea5d5c6dc0865</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Gateway</t>
+          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Kankakee, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b72e865e6bee153</t>
+          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189118b38618a67d</t>
+          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Nashville, TN</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>vectorsoft</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740c3688a7f68b22</t>
+          <t>https://www.indeed.com/viewjob?jk=3bdce3e69ca5f6c4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Implementation Consultant</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21788e731c4ee67c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb3e3385b26a0b5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - Cloud Gateway</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DASi LLC</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744c7eb16a44dfd7</t>
+          <t>https://www.indeed.com/viewjob?jk=7b72e865e6bee153</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=182574da3c06479e</t>
+          <t>https://www.indeed.com/viewjob?jk=189118b38618a67d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>data engineer sr- ST; Nashville, TN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61fd67550df6c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=740c3688a7f68b22</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Sr Implementation Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59fae488bfb069d7</t>
+          <t>https://www.indeed.com/viewjob?jk=21788e731c4ee67c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>DASi LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c511d00669b005c9</t>
+          <t>https://www.indeed.com/viewjob?jk=744c7eb16a44dfd7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Mustang Cat</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e02714fa8eb1d57</t>
+          <t>https://www.indeed.com/viewjob?jk=182574da3c06479e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf0feb71fccf2a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b61fd67550df6c0b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineering - E&amp;P - Data Integration Engineer I</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=59fae488bfb069d7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
+          <t>https://www.indeed.com/viewjob?jk=c511d00669b005c9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
+          <t>https://www.indeed.com/viewjob?jk=9e02714fa8eb1d57</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Laural Parke</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19dac2449c2108f4</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf0feb71fccf2a0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>Data Engineering - E&amp;P - Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Revelation Pharma</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265eee1218fa6fae</t>
+          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f621c8ad4f69fd</t>
+          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ce310e3e5771dd</t>
+          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Networking Consultant</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>DevOps / AgentOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Revelation Pharma</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
+          <t>https://www.indeed.com/viewjob?jk=265eee1218fa6fae</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f621c8ad4f69fd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ce310e3e5771dd</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- MSI</t>
+          <t>Cloud Networking Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
+          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Software Systems and Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b5659a9dfdc90</t>
+          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, Tableau, CI/CD</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ba967c2292803c</t>
+          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Entry-Level Cloud Engineering Specialist</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d9f4abcf179d24</t>
+          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390498da25e9e01</t>
+          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SSIS / Azure Data Factory Engineer</t>
+          <t>Senior Data Engineer- MSI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c3cae0c83282a2</t>
+          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>Sr. Software Systems and Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tardus inc</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c45bbb6f084151</t>
+          <t>https://www.indeed.com/viewjob?jk=606b5659a9dfdc90</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Biloxi 5139</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Keesler Federal Credit Union</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Biloxi, MS, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=923871eb4e708d96</t>
+          <t>https://www.indeed.com/viewjob?jk=57ba967c2292803c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Entry-Level Cloud Engineering Specialist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
+          <t>https://www.indeed.com/viewjob?jk=43d9f4abcf179d24</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Platform Engineer IV</t>
+          <t>Data Scientist, AI Data Foundations</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=2390498da25e9e01</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data intelligence</t>
+          <t>SSIS / Azure Data Factory Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
+          <t>https://www.indeed.com/viewjob?jk=85c3cae0c83282a2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IT/OT Data Engineer</t>
+          <t>Data Engineer with Python</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>Tardus inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c53f35832dc5e29</t>
+          <t>https://www.indeed.com/viewjob?jk=80c45bbb6f084151</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer Biloxi 5139</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mesa Labs</t>
+          <t>Keesler Federal Credit Union</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Biloxi, MS, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d54ee3197b525a</t>
+          <t>https://www.indeed.com/viewjob?jk=923871eb4e708d96</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps Mobile</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
+          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>Data Platform Engineer IV</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Senior Software Engineer - Data intelligence</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,112 +2866,112 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76b38f99ba86c67f</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure &amp; AI Operations Engineer</t>
+          <t>IT/OT Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Pioneer Circuits Inc.</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccde5a1faa24e424</t>
+          <t>https://www.indeed.com/viewjob?jk=3c53f35832dc5e29</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Amer Technology, Inc</t>
+          <t>Mesa Labs</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b3557dd6a86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=71d54ee3197b525a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3ffcafc747cce2</t>
+          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
+          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>Data Scientist, AI Data Foundations</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
+          <t>https://www.indeed.com/viewjob?jk=76b38f99ba86c67f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer II- Front end/DevOps</t>
+          <t>Cloud Infrastructure &amp; AI Operations Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Pioneer Circuits Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Docker, Kubernetes, Git, Bitbucket, CloudWatch</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2a81785b048298</t>
+          <t>https://www.indeed.com/viewjob?jk=ccde5a1faa24e424</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Amer Technology, Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, PostgreSQL, MySQL, MongoDB, Docker, Git, Python</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8a3b04afc12b14</t>
+          <t>https://www.indeed.com/viewjob?jk=46b3557dd6a86d77</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Integration Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b035b944f2ad4c37</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3ffcafc747cce2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Integration Software Engineer</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba6e4aacd5b6631</t>
+          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Integration Software Engineer</t>
+          <t>Advisor Solution Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c7e0f49df408be</t>
+          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Integration Software Engineer</t>
+          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93164fc43ac74193</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Integration Software Engineer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12a4fd124772d9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Integration Software Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c38e2fae9b46f905</t>
+          <t>https://www.indeed.com/viewjob?jk=64300e27d0c96342</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>AI Research Scientist</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c35e0e10bd4748</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Track 25 LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
+          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer II- Front end/DevOps</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Docker, Kubernetes, Git, Bitbucket, CloudWatch</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2a81785b048298</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Onspring Technologies, LLC</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, Scala, PostgreSQL, MySQL, MongoDB, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8a3b04afc12b14</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Full-Stack (Factory Systems)</t>
+          <t>AI Application Developer III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68c700567606c4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI Application Developer III -Houston, TX</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e6c09a79e3dceb</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Applications Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SEEQ</t>
+          <t>Track 25 LLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ed320077d234a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Harman</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,15 +3671,400 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Onspring Technologies, LLC</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Full-Stack (Factory Systems)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68c700567606c4e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Data Integration Software Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b035b944f2ad4c37</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Data Integration Software Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ba6e4aacd5b6631</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Integration Software Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Portsmouth, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4c7e0f49df408be</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Data Integration Software Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Portsmouth, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93164fc43ac74193</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Data Integration Software Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12a4fd124772d9d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Data Integration Software Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c38e2fae9b46f905</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24e6c09a79e3dceb</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AI Applications Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SEEQ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02ed320077d234a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Engineer, AI</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Harman</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Novi, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4a91d05d9ba98a3a</t>
         </is>

--- a/results/job_matches_2026-05-07.xlsx
+++ b/results/job_matches_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer- Local</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a4e4b94b73fdc3</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbfa76f2864991e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Data Engineer- Local</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JCPenney</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2579776810e54bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=98a4e4b94b73fdc3</t>
         </is>
       </c>
     </row>
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d51b3269206c63f</t>
+          <t>https://www.indeed.com/viewjob?jk=2579776810e54bb8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JCPenney</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4c4141e761a1d57</t>
+          <t>https://www.indeed.com/viewjob?jk=3d51b3269206c63f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Compliance, Senior Backend Engineer (Java &amp; ETL Specialist), Dallas, Associate</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21fade0470597e2</t>
+          <t>https://www.indeed.com/viewjob?jk=b4c4141e761a1d57</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Compliance, Senior Backend Engineer (Java &amp; ETL Specialist), Dallas, Associate</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
+          <t>https://www.indeed.com/viewjob?jk=e21fade0470597e2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
+          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>AI Research Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
+          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
+          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Engineer</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448348a55cfb6b88</t>
+          <t>https://www.indeed.com/viewjob?jk=2490ff4694380e91</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2490ff4694380e91</t>
+          <t>https://www.indeed.com/viewjob?jk=c43843e3963f6e92</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Software Engineer II - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,77 +1081,77 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Scala, Splunk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43843e3963f6e92</t>
+          <t>https://www.indeed.com/viewjob?jk=448348a55cfb6b88</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cambridge Mobile Telematics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Cambridge Mobile Telematics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
+          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c3ebd29f25c3c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb9808701c11641</t>
+          <t>https://www.indeed.com/viewjob?jk=0c3ebd29f25c3c6c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb9808701c11641</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Data engineer with Snowflake AND Databricks</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb10f4ead0ebaa8c</t>
+          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
+          <t>https://www.indeed.com/viewjob?jk=bb10f4ead0ebaa8c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
+          <t>Senior Data analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Mid- Level Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cloud Ramp</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=015ea5d5c6dc0865</t>
+          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
+          <t>Advancement Cloud Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kankakee, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
+          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
+          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Technical/User support</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>vectorsoft</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bdce3e69ca5f6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cloud Ramp</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb3e3385b26a0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=015ea5d5c6dc0865</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Gateway</t>
+          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Kankakee, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b72e865e6bee153</t>
+          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189118b38618a67d</t>
+          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Nashville, TN</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>vectorsoft</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740c3688a7f68b22</t>
+          <t>https://www.indeed.com/viewjob?jk=3bdce3e69ca5f6c4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Implementation Consultant</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21788e731c4ee67c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb3e3385b26a0b5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DASi LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744c7eb16a44dfd7</t>
+          <t>https://www.indeed.com/viewjob?jk=189118b38618a67d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>data engineer sr- ST; Nashville, TN</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=182574da3c06479e</t>
+          <t>https://www.indeed.com/viewjob?jk=740c3688a7f68b22</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>DASi LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61fd67550df6c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=744c7eb16a44dfd7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Mustang Cat</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59fae488bfb069d7</t>
+          <t>https://www.indeed.com/viewjob?jk=182574da3c06479e</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c511d00669b005c9</t>
+          <t>https://www.indeed.com/viewjob?jk=b61fd67550df6c0b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e02714fa8eb1d57</t>
+          <t>https://www.indeed.com/viewjob?jk=59fae488bfb069d7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf0feb71fccf2a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c511d00669b005c9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineering - E&amp;P - Data Integration Engineer I</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=9e02714fa8eb1d57</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf0feb71fccf2a0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Engineering - E&amp;P - Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
+          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Revelation Pharma</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265eee1218fa6fae</t>
+          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>DevOps / AgentOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Revelation Pharma</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f621c8ad4f69fd</t>
+          <t>https://www.indeed.com/viewjob?jk=265eee1218fa6fae</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ce310e3e5771dd</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,77 +2306,77 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
+          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Senior Data Engineer- MSI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
+          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Sr. Software Systems and Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=606b5659a9dfdc90</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
+          <t>https://www.indeed.com/viewjob?jk=57ba967c2292803c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- MSI</t>
+          <t>Entry-Level Cloud Engineering Specialist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
+          <t>https://www.indeed.com/viewjob?jk=43d9f4abcf179d24</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Software Systems and Data Engineer</t>
+          <t>Data Scientist, AI Data Foundations</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b5659a9dfdc90</t>
+          <t>https://www.indeed.com/viewjob?jk=2390498da25e9e01</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SSIS / Azure Data Factory Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ba967c2292803c</t>
+          <t>https://www.indeed.com/viewjob?jk=85c3cae0c83282a2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Entry-Level Cloud Engineering Specialist</t>
+          <t>Data Engineer with Python</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Tardus inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d9f4abcf179d24</t>
+          <t>https://www.indeed.com/viewjob?jk=80c45bbb6f084151</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>Senior Data Engineer Biloxi 5139</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Keesler Federal Credit Union</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Biloxi, MS, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390498da25e9e01</t>
+          <t>https://www.indeed.com/viewjob?jk=923871eb4e708d96</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SSIS / Azure Data Factory Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c3cae0c83282a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tardus inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c45bbb6f084151</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Biloxi 5139</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Keesler Federal Credit Union</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Biloxi, MS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=923871eb4e708d96</t>
+          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer IV</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prometheus Security Group Global</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, Azure, GCP, Hadoop, HDFS, Scala, Kafka, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
+          <t>https://www.indeed.com/viewjob?jk=532a5dc115e85e1e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Software Engineer - Data intelligence</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Platform Engineer IV</t>
+          <t>IT/OT Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Merz Aesthetics</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Racine, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=3c53f35832dc5e29</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data intelligence</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Mesa Labs</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
+          <t>https://www.indeed.com/viewjob?jk=71d54ee3197b525a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IT/OT Data Engineer</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c53f35832dc5e29</t>
+          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mesa Labs</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d54ee3197b525a</t>
+          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Data Scientist, AI Data Foundations</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
+          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,94 +3016,94 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
+          <t>https://www.indeed.com/viewjob?jk=76b38f99ba86c67f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=202bf089bcecf5fb</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Cloud Infrastructure &amp; AI Operations Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Pioneer Circuits Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76b38f99ba86c67f</t>
+          <t>https://www.indeed.com/viewjob?jk=ccde5a1faa24e424</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure &amp; AI Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pioneer Circuits Inc.</t>
+          <t>Amer Technology, Inc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccde5a1faa24e424</t>
+          <t>https://www.indeed.com/viewjob?jk=46b3557dd6a86d77</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Amer Technology, Inc</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b3557dd6a86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Advisor Solution Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3ffcafc747cce2</t>
+          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
+          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
+          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>AI Application Developer III</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
+          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>AI Application Developer III -Houston, TX</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64300e27d0c96342</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Track 25 LLC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c35e0e10bd4748</t>
+          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Onspring Technologies, LLC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer II- Front end/DevOps</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Docker, Kubernetes, Git, Bitbucket, CloudWatch</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2a81785b048298</t>
+          <t>https://www.indeed.com/viewjob?jk=24e6c09a79e3dceb</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Senior Engineer, AI</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Harman</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Novi, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,540 +3531,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, PostgreSQL, MySQL, MongoDB, Docker, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8a3b04afc12b14</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>AI Application Developer III</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Love’s Travel Stops</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>AI Application Developer III -Houston, TX</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Love’s Travel Stops</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Track 25 LLC</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Mesa, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Litera</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Onspring Technologies, LLC</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Full-Stack (Factory Systems)</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68c700567606c4e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b035b944f2ad4c37</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba6e4aacd5b6631</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Portsmouth, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c7e0f49df408be</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Portsmouth, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93164fc43ac74193</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12a4fd124772d9d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c38e2fae9b46f905</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Mastercard</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24e6c09a79e3dceb</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>AI Applications Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>SEEQ</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02ed320077d234a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Engineer, AI</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Harman</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Novi, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4a91d05d9ba98a3a</t>
         </is>

--- a/results/job_matches_2026-05-07.xlsx
+++ b/results/job_matches_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineering - E&amp;P - Data Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -573,52 +573,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Azure, Databricks</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9377a4724bf38c</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbfa76f2864991e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer- Local</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbfa76f2864991e</t>
+          <t>https://www.indeed.com/viewjob?jk=98a4e4b94b73fdc3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer- Local</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>JCPenney</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a4e4b94b73fdc3</t>
+          <t>https://www.indeed.com/viewjob?jk=2579776810e54bb8</t>
         </is>
       </c>
     </row>
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2579776810e54bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d51b3269206c63f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JCPenney</t>
+          <t>UCCU</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d51b3269206c63f</t>
+          <t>https://www.indeed.com/viewjob?jk=0442b12c52280bd2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Compliance, Senior Backend Engineer (Java &amp; ETL Specialist), Dallas, Associate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4c4141e761a1d57</t>
+          <t>https://www.indeed.com/viewjob?jk=e21fade0470597e2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Compliance, Senior Backend Engineer (Java &amp; ETL Specialist), Dallas, Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21fade0470597e2</t>
+          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Research Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
+          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
+          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
+          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>DevOps Engineer, Surveillance</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cambridge Mobile Telematics</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
+          <t>https://www.indeed.com/viewjob?jk=432c12682fbcbbc1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Cambridge Mobile Telematics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
+          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c3ebd29f25c3c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb9808701c11641</t>
+          <t>https://www.indeed.com/viewjob?jk=0c3ebd29f25c3c6c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data engineer with Snowflake AND Databricks</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb9808701c11641</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Data engineer with Snowflake AND Databricks</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb10f4ead0ebaa8c</t>
+          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
         </is>
       </c>
     </row>
@@ -1348,20 +1348,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>You.com</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
+          <t>https://www.indeed.com/viewjob?jk=bb10f4ead0ebaa8c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data analyst</t>
+          <t>Advancement Cloud Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
+          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Advancement Cloud Engineer II</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,94 +1546,94 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer - Technical/User support</t>
+          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
+          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Application Developer 2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cloud Ramp</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=015ea5d5c6dc0865</t>
+          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
+          <t>Data Engineer - Technical/User support</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kankakee, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Cloud Ramp</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
+          <t>https://www.indeed.com/viewjob?jk=015ea5d5c6dc0865</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>vectorsoft</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kankakee, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bdce3e69ca5f6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb3e3385b26a0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
         </is>
       </c>
     </row>
@@ -2043,25 +2043,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Grid Elevated</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, API Gateway, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf0feb71fccf2a0</t>
+          <t>https://www.indeed.com/viewjob?jk=a0d3426744c1c66f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineering - E&amp;P - Data Integration Engineer I</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>Cloaked</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf0feb71fccf2a0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2253,7 +2253,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Networking Consultant</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
+          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Backblaze</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
+          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,24 +2621,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
+          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Platform Engineer IV</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Platform Engineer IV</t>
+          <t>Senior Software Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mesa Labs</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d54ee3197b525a</t>
+          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
+          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
+          <t>Data Scientist, AI Data Foundations</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,77 +2946,77 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
+          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>Software Engineer III/Senior, Data Platform</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76b38f99ba86c67f</t>
+          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Java/ Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Marathon TS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,14 +3226,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
+          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
+          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
+          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>AI Application Developer III</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
+          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Application Developer III -Houston, TX</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Track 25 LLC</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>Track 25 LLC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
+          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Onspring Technologies, LLC</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
         </is>
       </c>
     </row>
@@ -3507,41 +3507,6 @@
       <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=24e6c09a79e3dceb</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Engineer, AI</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Harman</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Novi, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a91d05d9ba98a3a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-07.xlsx
+++ b/results/job_matches_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AMB Sports + Entertainment</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fac751a341ffed9</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1b4aa287718cb7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1b4aa287718cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=7283c54206f1c1eb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Data / Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Excel Services Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7283c54206f1c1eb</t>
+          <t>https://www.indeed.com/viewjob?jk=6aded2448d39f359</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JCPenney</t>
+          <t>Catalyst Brands</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JCPenney</t>
+          <t>Catalyst Brands</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Compliance, Senior Backend Engineer (Java &amp; ETL Specialist), Dallas, Associate</t>
+          <t>Senior Infrastructure</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Crackajack Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21fade0470597e2</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0aa2c9b63c9375</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Compliance, Senior Backend Engineer (Java &amp; ETL Specialist), Dallas, Associate</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
+          <t>https://www.indeed.com/viewjob?jk=e21fade0470597e2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
+          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>AI Research Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
+          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Surveillance</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,29 +976,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
+          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>DevOps Engineer, Surveillance</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2490ff4694380e91</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43843e3963f6e92</t>
+          <t>https://www.indeed.com/viewjob?jk=2490ff4694380e91</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Engineer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Scala, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448348a55cfb6b88</t>
+          <t>https://www.indeed.com/viewjob?jk=c43843e3963f6e92</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Software Engineer II - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Scala, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
+          <t>https://www.indeed.com/viewjob?jk=448348a55cfb6b88</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, MySQL, Cassandra</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432c12682fbcbbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cambridge Mobile Telematics</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,77 +1186,77 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
+          <t>https://www.indeed.com/viewjob?jk=3ffbea23a61e7b59</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
+          <t>https://www.indeed.com/viewjob?jk=432c12682fbcbbc1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Cambridge Mobile Telematics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c3ebd29f25c3c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb9808701c11641</t>
+          <t>https://www.indeed.com/viewjob?jk=0c3ebd29f25c3c6c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data engineer with Snowflake AND Databricks</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb9808701c11641</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data engineer with Snowflake AND Databricks</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>You.com</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
+          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>You.com</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb10f4ead0ebaa8c</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Advancement Cloud Engineer II</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
+          <t>https://www.indeed.com/viewjob?jk=bb10f4ead0ebaa8c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Automation Engineer IV</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Airlines Reporting Corporation (ARC)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
+          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Advancement Cloud Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Application Developer 2</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,104 +1606,104 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - Technical/User support</t>
+          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
+          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Application Developer 2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cloud Ramp</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=015ea5d5c6dc0865</t>
+          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
+          <t>Data Engineer - Technical/User support</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kankakee, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Cloud Ramp</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
+          <t>https://www.indeed.com/viewjob?jk=015ea5d5c6dc0865</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Kankakee, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189118b38618a67d</t>
+          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Nashville, TN</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740c3688a7f68b22</t>
+          <t>https://www.indeed.com/viewjob?jk=189118b38618a67d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>data engineer sr- ST; Nashville, TN</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DASi LLC</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744c7eb16a44dfd7</t>
+          <t>https://www.indeed.com/viewjob?jk=740c3688a7f68b22</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>Gerber Childrenswear, Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=182574da3c06479e</t>
+          <t>https://www.indeed.com/viewjob?jk=851b03fb4ff62f20</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>DASi LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61fd67550df6c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=744c7eb16a44dfd7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Mustang Cat</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59fae488bfb069d7</t>
+          <t>https://www.indeed.com/viewjob?jk=182574da3c06479e</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c511d00669b005c9</t>
+          <t>https://www.indeed.com/viewjob?jk=b61fd67550df6c0b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e02714fa8eb1d57</t>
+          <t>https://www.indeed.com/viewjob?jk=59fae488bfb069d7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Grid Elevated</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,77 +2061,77 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, API Gateway, IAM, Scala, DynamoDB</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0d3426744c1c66f</t>
+          <t>https://www.indeed.com/viewjob?jk=c511d00669b005c9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cloaked</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
+          <t>https://www.indeed.com/viewjob?jk=9e02714fa8eb1d57</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Grid Elevated</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, API Gateway, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf0feb71fccf2a0</t>
+          <t>https://www.indeed.com/viewjob?jk=a0d3426744c1c66f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>TopStep</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Revelation Pharma</t>
+          <t>Cloaked</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265eee1218fa6fae</t>
+          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf0feb71fccf2a0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
+          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Backblaze</t>
+          <t>Future Secure AI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=faa6451e47d9dd5e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- MSI</t>
+          <t>DevOps / AgentOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>Revelation Pharma</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,94 +2351,94 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
+          <t>https://www.indeed.com/viewjob?jk=265eee1218fa6fae</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Software Systems and Data Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b5659a9dfdc90</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, Tableau, CI/CD</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ba967c2292803c</t>
+          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Entry-Level Cloud Engineering Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d9f4abcf179d24</t>
+          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Backblaze</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,29 +2481,29 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390498da25e9e01</t>
+          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SSIS / Azure Data Factory Engineer</t>
+          <t>Senior Data Engineer- MSI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c3cae0c83282a2</t>
+          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>Sr. Software Systems and Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tardus inc</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c45bbb6f084151</t>
+          <t>https://www.indeed.com/viewjob?jk=606b5659a9dfdc90</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Biloxi 5139</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Keesler Federal Credit Union</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Biloxi, MS, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=923871eb4e708d96</t>
+          <t>https://www.indeed.com/viewjob?jk=57ba967c2292803c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Entry-Level Cloud Engineering Specialist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
+          <t>https://www.indeed.com/viewjob?jk=43d9f4abcf179d24</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Scientist, AI Data Foundations</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=2390498da25e9e01</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Platform Engineer IV</t>
+          <t>SSIS / Azure Data Factory Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=85c3cae0c83282a2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (5+ years)</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Prometheus Security Group Global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Hadoop, HDFS, Scala, Kafka, CI/CD, Maven</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=532a5dc115e85e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data intelligence</t>
+          <t>Data Platform Engineer IV</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
+          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IT/OT Data Engineer</t>
+          <t>Senior Software Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Merz Aesthetics</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Spark, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c53f35832dc5e29</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Prometheus Security Group Global</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, ECS, Azure, GCP, Hadoop, HDFS, Scala, Kafka, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
+          <t>https://www.indeed.com/viewjob?jk=532a5dc115e85e1e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
+          <t>Senior Software Engineer - Data intelligence</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,102 +2946,102 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer III/Senior, Data Platform</t>
+          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
+          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Data Scientist, AI Data Foundations</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
+          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=202bf089bcecf5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure &amp; AI Operations Engineer</t>
+          <t>Software Engineer III/Senior, Data Platform</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Pioneer Circuits Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccde5a1faa24e424</t>
+          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Amer Technology, Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b3557dd6a86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
+          <t>https://www.indeed.com/viewjob?jk=202bf089bcecf5fb</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>Cloud Infrastructure &amp; AI Operations Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Pioneer Circuits Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=ccde5a1faa24e424</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Java/ Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Marathon TS</t>
+          <t>Amer Technology, Inc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
+          <t>https://www.indeed.com/viewjob?jk=46b3557dd6a86d77</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8b3afa900ba086</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
+          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
+          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>Advisor Solution Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
+          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Verse</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, dbt, MLOps, CI/CD, Airflow, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
+          <t>https://www.indeed.com/viewjob?jk=595f48c6de986c3b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Java/ Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Track 25 LLC</t>
+          <t>Marathon TS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
+          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
+          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,262 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>AI Application Developer III</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Love’s Travel Stops</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>AI Application Developer III -Houston, TX</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Love’s Travel Stops</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Track 25 LLC</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Mesa, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=24e6c09a79e3dceb</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Software Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Software Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-07.xlsx
+++ b/results/job_matches_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Infrastructure</t>
+          <t>Senior Data Engineer - AI Program</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Crackajack Solutions</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Oracle</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0aa2c9b63c9375</t>
+          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Compliance, Senior Backend Engineer (Java &amp; ETL Specialist), Dallas, Associate</t>
+          <t>Senior Infrastructure</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Crackajack Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21fade0470597e2</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0aa2c9b63c9375</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Research Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
+          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
+          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
+          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>DevOps Engineer, Surveillance</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,29 +976,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Surveillance</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
+          <t>https://www.indeed.com/viewjob?jk=2490ff4694380e91</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2490ff4694380e91</t>
+          <t>https://www.indeed.com/viewjob?jk=c43843e3963f6e92</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Software Engineer II - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Scala, Splunk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43843e3963f6e92</t>
+          <t>https://www.indeed.com/viewjob?jk=448348a55cfb6b88</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Scala, Splunk</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448348a55cfb6b88</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Kikoff</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, MySQL, Cassandra</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432c12682fbcbbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=a7dd0cd975d51e1d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cambridge Mobile Telematics</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
+          <t>https://www.indeed.com/viewjob?jk=432c12682fbcbbc1</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps Automation Engineer IV</t>
+          <t>Data Engineer II - Snowflake AI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Airlines Reporting Corporation (ARC)</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Advancement Cloud Engineer II</t>
+          <t>DevOps Automation Engineer IV</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Airlines Reporting Corporation (ARC)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
+          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Advancement Cloud Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
+          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Application Developer 2</t>
+          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer - Technical/User support</t>
+          <t>Application Developer 2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
+          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Senior Software Engineer - AI Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cloud Ramp</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=015ea5d5c6dc0865</t>
+          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kankakee, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
+          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189118b38618a67d</t>
+          <t>https://www.indeed.com/viewjob?jk=7117100363dcdf16</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Nashville, TN</t>
+          <t>Data Engineer - Technical/User support</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740c3688a7f68b22</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gerber Childrenswear, Inc</t>
+          <t>Cloud Ramp</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=851b03fb4ff62f20</t>
+          <t>https://www.indeed.com/viewjob?jk=015ea5d5c6dc0865</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DASi LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744c7eb16a44dfd7</t>
+          <t>https://www.indeed.com/viewjob?jk=189118b38618a67d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>data engineer sr- ST; Nashville, TN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=182574da3c06479e</t>
+          <t>https://www.indeed.com/viewjob?jk=740c3688a7f68b22</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>DASi LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61fd67550df6c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=744c7eb16a44dfd7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Mustang Cat</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59fae488bfb069d7</t>
+          <t>https://www.indeed.com/viewjob?jk=182574da3c06479e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Grid Elevated</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,77 +2061,77 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, API Gateway, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c511d00669b005c9</t>
+          <t>https://www.indeed.com/viewjob?jk=a0d3426744c1c66f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>TopStep</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e02714fa8eb1d57</t>
+          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Grid Elevated</t>
+          <t>Cloaked</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, API Gateway, IAM, Scala, DynamoDB</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0d3426744c1c66f</t>
+          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TopStep</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf0feb71fccf2a0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cloaked</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
+          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Future Secure AI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf0feb71fccf2a0</t>
+          <t>https://www.indeed.com/viewjob?jk=faa6451e47d9dd5e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Future Secure AI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa6451e47d9dd5e</t>
+          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Revelation Pharma</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265eee1218fa6fae</t>
+          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Backblaze</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,59 +2386,59 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
+          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Senior Data Engineer- MSI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
+          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Systems and Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=606b5659a9dfdc90</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Backblaze</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=57ba967c2292803c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- MSI</t>
+          <t>Entry-Level Cloud Engineering Specialist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
+          <t>https://www.indeed.com/viewjob?jk=43d9f4abcf179d24</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Software Systems and Data Engineer</t>
+          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b5659a9dfdc90</t>
+          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Asst Dir-Machine Learning Eng- Partnerships</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, Tableau, CI/CD</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ba967c2292803c</t>
+          <t>https://www.indeed.com/viewjob?jk=1e239f656b6d91ee</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Entry-Level Cloud Engineering Specialist</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d9f4abcf179d24</t>
+          <t>https://www.indeed.com/viewjob?jk=606ee7147f0424e1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390498da25e9e01</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SSIS / Azure Data Factory Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c3cae0c83282a2</t>
+          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Data Platform Engineer IV</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
+          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Platform Engineer IV</t>
+          <t>Senior Software Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (5+ years)</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Prometheus Security Group Global</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, Azure, GCP, Hadoop, HDFS, Scala, Kafka, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
+          <t>https://www.indeed.com/viewjob?jk=532a5dc115e85e1e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Senior Software Engineer - Data intelligence</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Prometheus Security Group Global</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Hadoop, HDFS, Scala, Kafka, CI/CD, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=532a5dc115e85e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data intelligence</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
+          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
+          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
+          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,77 +2971,77 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
+          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
+          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8b3afa900ba086</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8b3afa900ba086</t>
+          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Advisor Solution Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
+          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
+          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, dbt, MLOps, CI/CD, Airflow, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=595f48c6de986c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Java/ Machine Learning Engineer</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Marathon TS</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
+          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
+          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Senior Java/ Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Marathon TS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
+          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
+          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
+          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Application Developer III</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Track 25 LLC</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
+          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI Application Developer III -Houston, TX</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e6c09a79e3dceb</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Track 25 LLC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
+          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,17 +3741,52 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
+          <t>https://www.indeed.com/viewjob?jk=24e6c09a79e3dceb</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Verse</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, dbt, MLOps, CI/CD, Airflow, Python</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=595f48c6de986c3b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-07.xlsx
+++ b/results/job_matches_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>CLOUD SOLUTION ARCHITECT (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, API Gateway, ECS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1b4aa287718cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=7cc98bb631036b24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7283c54206f1c1eb</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1b4aa287718cb7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data / Cloud Engineer</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Excel Services Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aded2448d39f359</t>
+          <t>https://www.indeed.com/viewjob?jk=7283c54206f1c1eb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data / Cloud Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Excel Services Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbfa76f2864991e</t>
+          <t>https://www.indeed.com/viewjob?jk=6aded2448d39f359</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer- Local</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a4e4b94b73fdc3</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbfa76f2864991e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Data Engineer- Local</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Catalyst Brands</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2579776810e54bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=98a4e4b94b73fdc3</t>
         </is>
       </c>
     </row>
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d51b3269206c63f</t>
+          <t>https://www.indeed.com/viewjob?jk=2579776810e54bb8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UCCU</t>
+          <t>Catalyst Brands</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442b12c52280bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=3d51b3269206c63f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI Program</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>UCCU</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0442b12c52280bd2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Infrastructure</t>
+          <t>Senior Data Engineer - AI Program</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Crackajack Solutions</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Oracle</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0aa2c9b63c9375</t>
+          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>Senior Infrastructure</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Crackajack Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0aa2c9b63c9375</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>AI Research Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
+          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Surveillance</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
+          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Engineer</t>
+          <t>DevOps Engineer, Surveillance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Scala, Splunk</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448348a55cfb6b88</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Integration Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>Kikoff</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ffbea23a61e7b59</t>
+          <t>https://www.indeed.com/viewjob?jk=a7dd0cd975d51e1d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kikoff</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7dd0cd975d51e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>.NET Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, MySQL, Cassandra</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432c12682fbcbbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
+          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
+          <t>Application Developer 2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Application Developer 2</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>Verato</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, SQS, RDS, Kafka, Snowflake, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=5dc8cc7a510942d0</t>
         </is>
       </c>
     </row>
@@ -2008,60 +2008,60 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=182574da3c06479e</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Grid Elevated</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, API Gateway, IAM, Scala, DynamoDB</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0d3426744c1c66f</t>
+          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TopStep</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cloaked</t>
+          <t>TopStep</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
+          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Cloaked</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf0feb71fccf2a0</t>
+          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf0feb71fccf2a0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Future Secure AI</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa6451e47d9dd5e</t>
+          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Cloud DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
+          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Future Secure AI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
+          <t>https://www.indeed.com/viewjob?jk=faa6451e47d9dd5e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Test and Automation (Remote, US)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
+          <t>AWS, Lambda, S3, RDS, GCP, Scala, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=97cf888a72ff8c87</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Backblaze</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,59 +2386,59 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- MSI</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
+          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Software Systems and Data Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark, NoSQL</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606b5659a9dfdc90</t>
+          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ba967c2292803c</t>
+          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Entry-Level Cloud Engineering Specialist</t>
+          <t>Senior Engineer -Devops</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d9f4abcf179d24</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Celigo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
+          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Asst Dir-Machine Learning Eng- Partnerships</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e239f656b6d91ee</t>
+          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Backblaze</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606ee7147f0424e1</t>
+          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Data Engineer- MSI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
+          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=57ba967c2292803c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Platform Engineer IV</t>
+          <t>Entry-Level Cloud Engineering Specialist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=43d9f4abcf179d24</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (5+ years)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
+          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Data Platform Engineer IV</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Prometheus Security Group Global</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Hadoop, HDFS, Scala, Kafka, CI/CD, Maven</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=532a5dc115e85e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data intelligence</t>
+          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
+          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
+          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Asst Dir-Machine Learning Eng- Partnerships</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
+          <t>https://www.indeed.com/viewjob?jk=1e239f656b6d91ee</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
+          <t>https://www.indeed.com/viewjob?jk=606ee7147f0424e1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
+          <t>Senior Software Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Prometheus Security Group Global</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, ECS, Azure, GCP, Hadoop, HDFS, Scala, Kafka, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8b3afa900ba086</t>
+          <t>https://www.indeed.com/viewjob?jk=532a5dc115e85e1e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
+          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer III/Senior, Data Platform</t>
+          <t>Engineer - Integrations</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb6fedab2823a33a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior Software Engineer - Data intelligence</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,67 +3121,67 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=202bf089bcecf5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure &amp; AI Operations Engineer</t>
+          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pioneer Circuits Inc.</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccde5a1faa24e424</t>
+          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java, Pyspark Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Amer Technology, Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b3557dd6a86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8b3afa900ba086</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer III/Senior, Data Platform</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
+          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
+          <t>https://www.indeed.com/viewjob?jk=202bf089bcecf5fb</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Cloud Infrastructure &amp; AI Operations Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Pioneer Circuits Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
+          <t>https://www.indeed.com/viewjob?jk=ccde5a1faa24e424</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Amer Technology, Inc</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
+          <t>https://www.indeed.com/viewjob?jk=46b3557dd6a86d77</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Java/ Machine Learning Engineer</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Marathon TS</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
+          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Advisor Solution Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
+          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
+          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
+          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
+          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Track 25 LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
+          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Java/ Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Marathon TS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e6c09a79e3dceb</t>
+          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,15 +3776,225 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>LLM Application Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AI Application Developer III</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Love’s Travel Stops</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AI Application Developer III -Houston, TX</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Love’s Travel Stops</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Track 25 LLC</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Mesa, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Verse</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>AWS, Azure, GCP, Scala, Data Modeling, dbt, MLOps, CI/CD, Airflow, Python</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=595f48c6de986c3b</t>
         </is>

--- a/results/job_matches_2026-05-07.xlsx
+++ b/results/job_matches_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Google Cloud Data Architect – IAM Data Modernization</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbfa76f2864991e</t>
+          <t>https://www.indeed.com/viewjob?jk=83f62e0d739d27aa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer- Local</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a4e4b94b73fdc3</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbfa76f2864991e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Data Engineer- Local</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Catalyst Brands</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2579776810e54bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=98a4e4b94b73fdc3</t>
         </is>
       </c>
     </row>
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d51b3269206c63f</t>
+          <t>https://www.indeed.com/viewjob?jk=2579776810e54bb8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UCCU</t>
+          <t>Catalyst Brands</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442b12c52280bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=3d51b3269206c63f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI Program</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>UCCU</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0442b12c52280bd2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Infrastructure</t>
+          <t>Senior Data Engineer - AI Program</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Crackajack Solutions</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Oracle</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0aa2c9b63c9375</t>
+          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>DevOps Engineer, Surveillance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
+          <t>https://www.indeed.com/viewjob?jk=2490ff4694380e91</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=c43843e3963f6e92</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2490ff4694380e91</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43843e3963f6e92</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Surveillance</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Progress Residential</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,102 +1126,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
+          <t>https://www.indeed.com/viewjob?jk=42e8e88ca3fb6ab8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0c3ebd29f25c3c6c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kikoff</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7dd0cd975d51e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb9808701c11641</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>.NET Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
+          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,94 +1266,94 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
+          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c3ebd29f25c3c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Data engineer with Snowflake AND Databricks</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb9808701c11641</t>
+          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data engineer with Snowflake AND Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>You.com</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>You.com</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
+          <t>https://www.indeed.com/viewjob?jk=bb10f4ead0ebaa8c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb10f4ead0ebaa8c</t>
+          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer II - Snowflake AI</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps Automation Engineer IV</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Airlines Reporting Corporation (ARC)</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Advancement Cloud Engineer II</t>
+          <t>Data Engineer II - Snowflake AI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Automation Engineer IV</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Airlines Reporting Corporation (ARC)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
+          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Advancement Cloud Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Application Developer 2</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,147 +1676,147 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Verato</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, RDS, Kafka, Snowflake, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dc8cc7a510942d0</t>
+          <t>https://www.indeed.com/viewjob?jk=41506061e08a6c6b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Platform</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f05c8dd67fcf30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>University Of Washington</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
+          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Application Developer 2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7117100363dcdf16</t>
+          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - Technical/User support</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Verato</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, RDS, Kafka, Snowflake, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
+          <t>https://www.indeed.com/viewjob?jk=5dc8cc7a510942d0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Senior Software Engineer - AI Platform</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cloud Ramp</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=015ea5d5c6dc0865</t>
+          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189118b38618a67d</t>
+          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Nashville, TN</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740c3688a7f68b22</t>
+          <t>https://www.indeed.com/viewjob?jk=7117100363dcdf16</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Technical/User support</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DASi LLC</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,42 +1991,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744c7eb16a44dfd7</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
+          <t>https://www.indeed.com/viewjob?jk=189118b38618a67d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>data engineer sr- ST; Nashville, TN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,59 +2071,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=740c3688a7f68b22</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>DASi LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=744c7eb16a44dfd7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TopStep</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cloaked</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
+          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf0feb71fccf2a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>TopStep</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer III</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Cloaked</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
+          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Future Secure AI</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa6451e47d9dd5e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf0feb71fccf2a0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Engineer, Test and Automation (Remote, US)</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, GCP, Scala, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cf888a72ff8c87</t>
+          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Cloud DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
+          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
+          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Engineer -Devops</t>
+          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
+          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Celigo</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
+          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer -Devops</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
+          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Backblaze</t>
+          <t>Celigo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- MSI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
+          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Backblaze</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ba967c2292803c</t>
+          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Entry-Level Cloud Engineering Specialist</t>
+          <t>Senior Data Engineer- MSI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d9f4abcf179d24</t>
+          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,24 +2761,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
+          <t>https://www.indeed.com/viewjob?jk=57ba967c2292803c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Platform Engineer IV</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Solution Architect-CSC Consultant</t>
+          <t>Data Platform Engineer IV</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, Talend, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47ff834230a7734</t>
+          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Asst Dir-Machine Learning Eng- Partnerships</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e239f656b6d91ee</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606ee7147f0424e1</t>
+          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (5+ years)</t>
+          <t>Senior Software Engineer - Data intelligence</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Prometheus Security Group Global</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Hadoop, HDFS, Scala, Kafka, CI/CD, Maven</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=532a5dc115e85e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
+          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Engineer - Integrations</t>
+          <t>Senior Software Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb6fedab2823a33a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data intelligence</t>
+          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,67 +3121,67 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
+          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbdec210790339f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Java, Pyspark Developer</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8b3afa900ba086</t>
+          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
+          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer III/Senior, Data Platform</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,19 +3331,19 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Java, Pyspark Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
+          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=202bf089bcecf5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8b3afa900ba086</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure &amp; AI Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pioneer Circuits Inc.</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccde5a1faa24e424</t>
+          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III/Senior, Data Platform</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Amer Technology, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b3557dd6a86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
+          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=202bf089bcecf5fb</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Cloud Infrastructure &amp; AI Operations Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Pioneer Circuits Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
+          <t>https://www.indeed.com/viewjob?jk=ccde5a1faa24e424</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Amer Technology, Inc</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=46b3557dd6a86d77</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
+          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Advisor Solution Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
+          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
+          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Java/ Machine Learning Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Marathon TS</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
+          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
+          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
+          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AI Application Developer III</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
+          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>AI Application Developer III -Houston, TX</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
+          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Track 25 LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
+          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Java/ Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>Marathon TS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, dbt, MLOps, CI/CD, Airflow, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,7 +3996,77 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=595f48c6de986c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>LLM Application Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-07.xlsx
+++ b/results/job_matches_2026-05-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Google Cloud Data Architect – IAM Data Modernization</t>
+          <t>Software Engineer Sr. Consultant , Fullstack/GenAI Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f62e0d739d27aa</t>
+          <t>https://www.indeed.com/viewjob?jk=35bee00fc4ccb280</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Google Cloud Data Architect – IAM Data Modernization</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbfa76f2864991e</t>
+          <t>https://www.indeed.com/viewjob?jk=83f62e0d739d27aa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer- Local</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a4e4b94b73fdc3</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbfa76f2864991e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Data Engineer- Local</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Catalyst Brands</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2579776810e54bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=98a4e4b94b73fdc3</t>
         </is>
       </c>
     </row>
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d51b3269206c63f</t>
+          <t>https://www.indeed.com/viewjob?jk=2579776810e54bb8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UCCU</t>
+          <t>Catalyst Brands</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442b12c52280bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=3d51b3269206c63f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI Program</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>UCCU</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,69 +836,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0442b12c52280bd2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Research Scientist</t>
+          <t>Senior Data Engineer - AI Program</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>Google Cloud Platform, GCP, Hive, Spark, Kafka, Snowflake, ELT, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
+          <t>https://www.indeed.com/viewjob?jk=93617218f60aa5b4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Surveillance</t>
+          <t>AWS Enterprise Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
+          <t>AWS, EMR, Redshift, Athena, S3, Hadoop, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a34b81d478ac1d3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>AI Research Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2490ff4694380e91</t>
+          <t>https://www.indeed.com/viewjob?jk=73a34a9520c8a4a5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43843e3963f6e92</t>
+          <t>https://www.indeed.com/viewjob?jk=2490ff4694380e91</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>DevOps Engineer, Surveillance</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, RDS, Databricks, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a679b465b6c33f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba128c0294d4379</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5ac75a162ba9ad</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Progress Residential</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e8e88ca3fb6ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa5908e0a6f244</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Softengine</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, Kafka, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c3ebd29f25c3c6c</t>
+          <t>https://www.indeed.com/viewjob?jk=871fae4a024977f1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb9808701c11641</t>
+          <t>https://www.indeed.com/viewjob?jk=801d9528f59b4278</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Progress Residential</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,102 +1231,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
+          <t>https://www.indeed.com/viewjob?jk=42e8e88ca3fb6ab8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
+          <t>https://www.indeed.com/viewjob?jk=0c3ebd29f25c3c6c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb9808701c11641</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data engineer with Snowflake AND Databricks</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KIZEN Technologies, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
+          <t>https://www.indeed.com/viewjob?jk=39e0729d312a0ecd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>.NET Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>You.com</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>API Gateway, RDS, Azure, Scala, Kafka, SQL Server, NoSQL, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
+          <t>https://www.indeed.com/viewjob?jk=be0e5cb9ff763e41</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb10f4ead0ebaa8c</t>
+          <t>https://www.indeed.com/viewjob?jk=258bc7844352c3f1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
+          <t>https://www.indeed.com/viewjob?jk=54745117d2d5b210</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Data engineer with Snowflake AND Databricks</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7351b5f44a3c15ba</t>
         </is>
       </c>
     </row>
@@ -1488,20 +1488,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>You.com</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3012f6c986c6af</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer II - Snowflake AI</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
+          <t>AWS, EMR, Lambda, S3, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb10f4ead0ebaa8c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Automation Engineer IV</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Airlines Reporting Corporation (ARC)</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a4cfbea75688c9ed</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Advancement Cloud Engineer II</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
+          <t>https://www.indeed.com/viewjob?jk=52f68931c99845d3</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
+          <t>https://www.indeed.com/viewjob?jk=626873a69ef4c8b2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer II - Snowflake AI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b44c5f00132c0a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>DevOps Automation Engineer IV</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Airlines Reporting Corporation (ARC)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41506061e08a6c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=199a554b26acb4f6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Advancement Cloud Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f05c8dd67fcf30</t>
+          <t>https://www.indeed.com/viewjob?jk=46a7512a19a0f2e7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Application Developer (Full Stack) - College of Arts and Sciences</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98feff1d77525ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2c93edd86822c1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Application Developer 2</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4e64b6ab31fd0a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Verato</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, RDS, Kafka, Snowflake, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,102 +1861,102 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dc8cc7a510942d0</t>
+          <t>https://www.indeed.com/viewjob?jk=783168b15946ba04</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Platform</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
+          <t>https://www.indeed.com/viewjob?jk=41506061e08a6c6b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f05c8dd67fcf30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Application Developer 2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7117100363dcdf16</t>
+          <t>https://www.indeed.com/viewjob?jk=341905de86352ef7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer - Technical/User support</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Verato</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, RDS, Kafka, Snowflake, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
+          <t>https://www.indeed.com/viewjob?jk=5dc8cc7a510942d0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer - AI Platform</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189118b38618a67d</t>
+          <t>https://www.indeed.com/viewjob?jk=a9520742b57bdbbf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Nashville, TN</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740c3688a7f68b22</t>
+          <t>https://www.indeed.com/viewjob?jk=94b5225f6d075163</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DASi LLC</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744c7eb16a44dfd7</t>
+          <t>https://www.indeed.com/viewjob?jk=7117100363dcdf16</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Technical/User support</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbb16a0dc8d7fce</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=189118b38618a67d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>data engineer sr- ST; Nashville, TN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,59 +2211,59 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=740c3688a7f68b22</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TopStep</t>
+          <t>DASi LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
+          <t>https://www.indeed.com/viewjob?jk=744c7eb16a44dfd7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cloaked</t>
+          <t>Motive</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b4df3933dd78a0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf0feb71fccf2a0</t>
+          <t>https://www.indeed.com/viewjob?jk=19b2722e44d39f3c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=b6ddbca14f940ab0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>TopStep</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
+          <t>https://www.indeed.com/viewjob?jk=6f03231d1386b02a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cloaked</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
+          <t>https://www.indeed.com/viewjob?jk=551cb213bc9bdebf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf0feb71fccf2a0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,42 +2481,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
+          <t>https://www.indeed.com/viewjob?jk=b4df3fe80aaf3c5c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
+          <t>Cloud DevSecOps Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=940eea1ae3941224</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior AI/ML Platform Engineer</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
+          <t>https://www.indeed.com/viewjob?jk=1febfbe512a25ee0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Engineer -Devops</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f372d79fc760e6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Celigo</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
+          <t>https://www.indeed.com/viewjob?jk=b92007092f3a111a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
+          <t>Hadoop, Hive, Sqoop, Oozie, YARN, Impala, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=1385059d3224b189</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior AWS Serverless Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Backblaze</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=2a595e9aba40b0b9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- MSI</t>
+          <t>Senior Data Engineer – Enterprise Data Frameworks (Java Spark Focus)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, RDS, Spark, Scala, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
+          <t>https://www.indeed.com/viewjob?jk=eca9f093e2f385f4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ba967c2292803c</t>
+          <t>https://www.indeed.com/viewjob?jk=d1f33e8f121963da</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Engineer -Devops</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ec559f61088931</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Celigo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, CI/CD, GitHub Actions, Airflow, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=6dff5e552658401c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Platform Engineer IV</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,29 +2866,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Snowflake, Data Modeling, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=9b34ebfa2f39b5d0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Backblaze</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
+          <t>https://www.indeed.com/viewjob?jk=df831ecf1efacc6b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior Data Engineer- MSI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Cancer Society</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
+          <t>https://www.indeed.com/viewjob?jk=3be75135cd536532</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
+          <t>https://www.indeed.com/viewjob?jk=57ba967c2292803c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3079c4c7ceb474</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Developer Sr</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, NoSQL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
+          <t>https://www.indeed.com/viewjob?jk=67b14047cf4b1b2b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (5+ years)</t>
+          <t>Data Platform Engineer IV</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
+          <t>https://www.indeed.com/viewjob?jk=8317877d96469a8f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba8e3de971eddef</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbdec210790339f</t>
+          <t>https://www.indeed.com/viewjob?jk=da194a7fdcf7abf8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Senior Software Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6352e6589be89b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Senior Software Engineer - Data intelligence</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd57b2f229ee99a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,67 +3261,67 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
+          <t>https://www.indeed.com/viewjob?jk=ac09ee4ae12cf692</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
+          <t>https://www.indeed.com/viewjob?jk=55020019de30ef6d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer I, CNN Digital Products and Services</t>
+          <t>Systems Developer (TS/SCI w/ Poly) - Bid role starting in 8-10 weeks</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, EMR, Hive, Spark, Scala, Oracle, MySQL, ETL, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=38053030970a8053</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Java, Pyspark Developer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbdec210790339f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8b3afa900ba086</t>
+          <t>https://www.indeed.com/viewjob?jk=5b9db141b7401478</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a165ea66f85e55</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer III/Senior, Data Platform</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=06681d5885df2a47</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
+          <t>https://www.indeed.com/viewjob?jk=9db6123d90e51635</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Engineer I, CNN Digital Products and Services</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=202bf089bcecf5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6c010abcc1b9ad</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure &amp; AI Operations Engineer</t>
+          <t>Java, Pyspark Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Pioneer Circuits Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,19 +3576,19 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccde5a1faa24e424</t>
+          <t>https://www.indeed.com/viewjob?jk=35d16e80a49bcc0f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Amer Technology, Inc</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b3557dd6a86d77</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8b3afa900ba086</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3a16438c1d377b13</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>Software Engineer III/Senior, Data Platform</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, Athena, IAM, RDS, Scala, Kafka, dbt, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=b26a34ae5eed7d2c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,19 +3716,19 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
+          <t>https://www.indeed.com/viewjob?jk=1949523741452b18</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=202bf089bcecf5fb</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Cloud Infrastructure &amp; AI Operations Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Pioneer Circuits Inc.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
+          <t>https://www.indeed.com/viewjob?jk=ccde5a1faa24e424</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amer Technology, Inc</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
+          <t>https://www.indeed.com/viewjob?jk=46b3557dd6a86d77</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
+          <t>https://www.indeed.com/viewjob?jk=545894faf57b95a0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
+          <t>https://www.indeed.com/viewjob?jk=93d7525ba31f9666</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Data Analyst &amp; GenAI Specialist, Enterprise AI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Hive, Scala, Power BI, Tableau, Git, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
+          <t>https://www.indeed.com/viewjob?jk=49a3c5ea9cc7a4b0</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer (HYBRID)</t>
+          <t>Research Fellow - Artificial Intelligence/Machine Learning</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Amherst, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Dask, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
+          <t>https://www.indeed.com/viewjob?jk=bae29c34d0c2ccf3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Java/ Machine Learning Engineer</t>
+          <t>Consultant, Data Management</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Marathon TS</t>
+          <t>Beghou Consulting</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Databricks, Snowflake, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
+          <t>https://www.indeed.com/viewjob?jk=f0f426e9aa3d054e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
+          <t>https://www.indeed.com/viewjob?jk=2982fc10e352a13b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Software Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,17 +4056,332 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97647ed49aa0bb5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Java/ Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Marathon TS</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Kafka, MLOps, MLflow, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4225155fc7f038aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03bec9675bef2c72</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>LLM Application Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ef6bd275c16f574</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0efd009ff873e29f</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AI Application Developer III</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Love’s Travel Stops</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=939860f4afab99be</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AI Application Developer III -Houston, TX</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Love’s Travel Stops</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ca2a8fac6aa1523</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63fe6bded9b00c94</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad89e30e39887ae9</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=858b0940cb76a93d</t>
         </is>
       </c>
     </row>
